--- a/WorkBot/main/data/orders/Keck's Food Service/Keck's Food Service_Bakery_20260531.xlsx
+++ b/WorkBot/main/data/orders/Keck's Food Service/Keck's Food Service_Bakery_20260531.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,6 +500,195 @@
         <v>217.6</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>126160</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Peanut Butter - Bulk</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>60.59</v>
+      </c>
+      <c r="E7" t="n">
+        <v>60.59</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>108920</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Seeds - Sesame</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>78.22</v>
+      </c>
+      <c r="E8" t="n">
+        <v>78.22</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>4100760</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Boston Coffee Cake - Apple Cinnamon</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>167.4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>4100870</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Boston Coffee Cake - Blueberry</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>57.91</v>
+      </c>
+      <c r="E10" t="n">
+        <v>115.82</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>4100860</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Boston Coffee Cake - Cinnamon Walnut</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>57.91</v>
+      </c>
+      <c r="E11" t="n">
+        <v>57.91</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>124560</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pristine -Dough Conditioner</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>148.07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>148.07</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>108900</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Seeds - Poppy</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>98.53</v>
+      </c>
+      <c r="E13" t="n">
+        <v>98.53</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>124440</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>8 Grain</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>70.52</v>
+      </c>
+      <c r="E14" t="n">
+        <v>211.56</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>141730</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Molasses</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="E15" t="n">
+        <v>141.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
